--- a/测试用例/祖研-黑龙江省中医医院（三辅院区）/处理后表格/6月__三辅社区、香坊中医院6月结款函.xlsx
+++ b/测试用例/祖研-黑龙江省中医医院（三辅院区）/处理后表格/6月__三辅社区、香坊中医院6月结款函.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="27945" windowHeight="11805"/>
   </bookViews>
   <sheets>
-    <sheet name="三辅社区、香坊中医院7月结款函" sheetId="2" r:id="rId1"/>
+    <sheet name="三辅社区、香坊中医院6月结款函" sheetId="2" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
@@ -32,13 +32,21 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
-    <t>三辅社区服务中心、哈尔滨市香坊区中医医院5月份结款通知函</t>
+    <t>三辅社区服务中心、哈尔滨市香坊区中医医院6月份结款通知函</t>
   </si>
   <si>
     <t>致：三辅社区服务中心、哈尔滨市香坊区中医医院</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <u/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>2026</t>
     </r>
     <r>
